--- a/_ANALISIS DE RIESGOS.xlsx
+++ b/_ANALISIS DE RIESGOS.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="612" yWindow="588" windowWidth="21852" windowHeight="8676"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
+    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
   <si>
     <t>RIESGO</t>
   </si>
@@ -179,65 +182,102 @@
   </si>
   <si>
     <t>pandemia repentina</t>
+  </si>
+  <si>
+    <t>Repercusión</t>
+  </si>
+  <si>
+    <t>Catastrófica</t>
+  </si>
+  <si>
+    <t>Crítico</t>
+  </si>
+  <si>
+    <t>Menor</t>
+  </si>
+  <si>
+    <t>Insignificante</t>
+  </si>
+  <si>
+    <t>Probabilidad</t>
+  </si>
+  <si>
+    <t>Frecuente</t>
+  </si>
+  <si>
+    <t>Probable</t>
+  </si>
+  <si>
+    <t>Remota</t>
+  </si>
+  <si>
+    <t>Improbable</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="9">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="&quot;Aptos Narrow&quot;"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <color theme="1" tint="0.14999847407452621"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="&quot;Aptos Narrow&quot;"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF000000"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF00FF00"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -245,9 +285,117 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.14999847407452621"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.14999847407452621"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
-    <border/>
+  <borders count="5">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -261,81 +409,126 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="54">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -343,7 +536,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -533,964 +726,992 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A3:K39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="91.25"/>
-    <col customWidth="1" min="4" max="4" width="14.5"/>
-    <col customWidth="1" min="5" max="5" width="4.88"/>
-    <col customWidth="1" min="6" max="6" width="15.0"/>
-    <col customWidth="1" min="7" max="7" width="5.25"/>
-    <col customWidth="1" min="8" max="8" width="26.25"/>
+    <col min="3" max="3" width="101.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3">
+    <row r="3" spans="1:11">
       <c r="C3" s="1"/>
     </row>
-    <row r="5">
-      <c r="B5" s="2"/>
-      <c r="C5" s="3" t="s">
+    <row r="5" spans="1:11" ht="13.8">
+      <c r="C5" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="F5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="6"/>
+      <c r="I5" s="3"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6">
-      <c r="B6" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="C6" s="8" t="s">
+    <row r="6" spans="1:11" ht="13.8">
+      <c r="B6" s="8">
+        <v>1</v>
+      </c>
+      <c r="C6" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="F6" s="10" t="s">
+      <c r="E6" s="4">
+        <v>3</v>
+      </c>
+      <c r="F6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="9">
-        <v>4.0</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" ref="H6:H39" si="1"> E6*G6</f>
+      <c r="G6" s="4">
+        <v>4</v>
+      </c>
+      <c r="H6" s="52">
+        <f t="shared" ref="H6:H39" si="0">E6*G6</f>
         <v>12</v>
       </c>
       <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="J6" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="13.8">
+      <c r="B7" s="6">
+        <v>2</v>
+      </c>
+      <c r="C7" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="F7" s="12" t="s">
+      <c r="E7" s="5">
+        <v>3</v>
+      </c>
+      <c r="F7" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="H7" s="11">
-        <f t="shared" si="1"/>
+      <c r="G7" s="5">
+        <v>2</v>
+      </c>
+      <c r="H7" s="53">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="C8" s="10" t="s">
+      <c r="J7" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="13.8">
+      <c r="B8" s="6">
+        <v>3</v>
+      </c>
+      <c r="C8" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="H8" s="11">
-        <f t="shared" si="1"/>
+      <c r="E8" s="4">
+        <v>2</v>
+      </c>
+      <c r="F8" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4">
+        <v>3</v>
+      </c>
+      <c r="H8" s="53">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="J8" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="13.8">
+      <c r="B9" s="6">
+        <v>4</v>
+      </c>
+      <c r="C9" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="H9" s="11">
-        <f t="shared" si="1"/>
+      <c r="E9" s="5">
+        <v>4</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="5">
+        <v>3</v>
+      </c>
+      <c r="H9" s="52">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="J9" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="13.8">
+      <c r="B10" s="6">
+        <v>5</v>
+      </c>
+      <c r="C10" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="9">
-        <v>4.0</v>
-      </c>
-      <c r="F10" s="10" t="s">
+      <c r="E10" s="4">
+        <v>4</v>
+      </c>
+      <c r="F10" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="9">
-        <v>5.0</v>
-      </c>
-      <c r="H10" s="11">
-        <f t="shared" si="1"/>
+      <c r="G10" s="4">
+        <v>5</v>
+      </c>
+      <c r="H10" s="52">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="J10" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="K10" s="28" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="13.8">
+      <c r="B11" s="6">
+        <v>6</v>
+      </c>
+      <c r="C11" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="13">
-        <v>5.0</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="H11" s="11">
-        <f t="shared" si="1"/>
+      <c r="E11" s="5">
+        <v>5</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="5">
+        <v>3</v>
+      </c>
+      <c r="H11" s="52">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="J11" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="K11" s="32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="13.8">
+      <c r="B12" s="6">
+        <v>7</v>
+      </c>
+      <c r="C12" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="F12" s="10" t="s">
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="9">
-        <v>4.0</v>
-      </c>
-      <c r="H12" s="11">
-        <f t="shared" si="1"/>
+      <c r="G12" s="4">
+        <v>4</v>
+      </c>
+      <c r="H12" s="53">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13">
-      <c r="B13" s="7">
-        <v>8.0</v>
-      </c>
-      <c r="C13" s="12" t="s">
+    <row r="13" spans="1:11" ht="13.8">
+      <c r="B13" s="6">
+        <v>8</v>
+      </c>
+      <c r="C13" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="H13" s="11">
-        <f t="shared" si="1"/>
+      <c r="E13" s="5">
+        <v>2</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="5">
+        <v>3</v>
+      </c>
+      <c r="H13" s="53">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:11" ht="13.8">
       <c r="A14" s="1"/>
-      <c r="B14" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="6">
+        <v>9</v>
+      </c>
+      <c r="C14" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="9">
-        <v>4.0</v>
-      </c>
-      <c r="F14" s="9" t="s">
+      <c r="E14" s="4">
+        <v>4</v>
+      </c>
+      <c r="F14" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="9">
-        <v>5.0</v>
-      </c>
-      <c r="H14" s="11">
-        <f t="shared" si="1"/>
+      <c r="G14" s="4">
+        <v>5</v>
+      </c>
+      <c r="H14" s="52">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15">
-      <c r="B15" s="7">
-        <v>10.0</v>
-      </c>
-      <c r="C15" s="13" t="s">
+    <row r="15" spans="1:11" ht="13.8">
+      <c r="B15" s="6">
+        <v>10</v>
+      </c>
+      <c r="C15" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="H15" s="11">
-        <f t="shared" si="1"/>
+      <c r="E15" s="5">
+        <v>3</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="5">
+        <v>3</v>
+      </c>
+      <c r="H15" s="53">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16">
-      <c r="B16" s="7">
-        <v>11.0</v>
-      </c>
-      <c r="C16" s="10" t="s">
+    <row r="16" spans="1:11" ht="13.8">
+      <c r="B16" s="6">
+        <v>11</v>
+      </c>
+      <c r="C16" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="F16" s="9" t="s">
+      <c r="E16" s="4">
+        <v>3</v>
+      </c>
+      <c r="F16" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="G16" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="H16" s="11">
-        <f t="shared" si="1"/>
+      <c r="G16" s="4">
+        <v>2</v>
+      </c>
+      <c r="H16" s="53">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17">
-      <c r="B17" s="7">
-        <v>12.0</v>
-      </c>
-      <c r="C17" s="12" t="s">
+    <row r="17" spans="2:11" ht="13.8">
+      <c r="B17" s="6">
+        <v>12</v>
+      </c>
+      <c r="C17" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="F17" s="13" t="s">
+      <c r="E17" s="5">
+        <v>2</v>
+      </c>
+      <c r="F17" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="H17" s="11">
-        <f t="shared" si="1"/>
+      <c r="G17" s="5">
+        <v>1</v>
+      </c>
+      <c r="H17" s="53">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18">
-      <c r="B18" s="7">
-        <v>13.0</v>
-      </c>
-      <c r="C18" s="9" t="s">
+    <row r="18" spans="2:11" ht="13.8">
+      <c r="B18" s="6">
+        <v>13</v>
+      </c>
+      <c r="C18" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="9">
-        <v>5.0</v>
-      </c>
-      <c r="F18" s="9" t="s">
+      <c r="E18" s="4">
+        <v>5</v>
+      </c>
+      <c r="F18" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="H18" s="11">
-        <f t="shared" si="1"/>
+      <c r="G18" s="4">
+        <v>1</v>
+      </c>
+      <c r="H18" s="53">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19">
-      <c r="B19" s="7">
-        <v>14.0</v>
-      </c>
-      <c r="C19" s="8" t="s">
+    <row r="19" spans="2:11" ht="13.8">
+      <c r="B19" s="6">
+        <v>14</v>
+      </c>
+      <c r="C19" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="H19" s="11">
-        <f t="shared" si="1"/>
+      <c r="E19" s="5">
+        <v>4</v>
+      </c>
+      <c r="F19" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="5">
+        <v>3</v>
+      </c>
+      <c r="H19" s="52">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20">
-      <c r="B20" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="C20" s="10" t="s">
+    <row r="20" spans="2:11" ht="13.8">
+      <c r="B20" s="6">
+        <v>15</v>
+      </c>
+      <c r="C20" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="F20" s="9" t="s">
+      <c r="E20" s="4">
+        <v>3</v>
+      </c>
+      <c r="F20" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="G20" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="H20" s="11">
-        <f t="shared" si="1"/>
+      <c r="G20" s="4">
+        <v>2</v>
+      </c>
+      <c r="H20" s="53">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21">
-      <c r="B21" s="7">
-        <v>16.0</v>
-      </c>
-      <c r="C21" s="8" t="s">
+    <row r="21" spans="2:11" ht="13.8">
+      <c r="B21" s="6">
+        <v>16</v>
+      </c>
+      <c r="C21" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="F21" s="13" t="s">
+      <c r="E21" s="5">
+        <v>3</v>
+      </c>
+      <c r="F21" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="13">
-        <v>5.0</v>
-      </c>
-      <c r="H21" s="11">
-        <f t="shared" si="1"/>
+      <c r="G21" s="5">
+        <v>5</v>
+      </c>
+      <c r="H21" s="52">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22">
-      <c r="B22" s="7">
-        <v>17.0</v>
-      </c>
-      <c r="C22" s="8" t="s">
+    <row r="22" spans="2:11" ht="13.8">
+      <c r="B22" s="6">
+        <v>17</v>
+      </c>
+      <c r="C22" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="9">
-        <v>4.0</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="H22" s="11">
-        <f t="shared" si="1"/>
+      <c r="E22" s="4">
+        <v>4</v>
+      </c>
+      <c r="F22" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="4">
+        <v>3</v>
+      </c>
+      <c r="H22" s="52">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23">
-      <c r="B23" s="7">
-        <v>18.0</v>
-      </c>
-      <c r="C23" s="12" t="s">
+    <row r="23" spans="2:11" ht="13.8">
+      <c r="B23" s="6">
+        <v>18</v>
+      </c>
+      <c r="C23" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="H23" s="11">
-        <f t="shared" si="1"/>
+      <c r="E23" s="5">
+        <v>3</v>
+      </c>
+      <c r="F23" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="5">
+        <v>3</v>
+      </c>
+      <c r="H23" s="53">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24">
-      <c r="B24" s="7">
-        <v>19.0</v>
-      </c>
-      <c r="C24" s="10" t="s">
+    <row r="24" spans="2:11" ht="13.8">
+      <c r="B24" s="6">
+        <v>19</v>
+      </c>
+      <c r="C24" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="F24" s="9" t="s">
+      <c r="E24" s="4">
+        <v>1</v>
+      </c>
+      <c r="F24" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="9">
-        <v>4.0</v>
-      </c>
-      <c r="H24" s="11">
-        <f t="shared" si="1"/>
+      <c r="G24" s="4">
+        <v>4</v>
+      </c>
+      <c r="H24" s="53">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25">
-      <c r="B25" s="7">
-        <v>20.0</v>
-      </c>
-      <c r="C25" s="12" t="s">
+    <row r="25" spans="2:11" ht="13.8">
+      <c r="B25" s="6">
+        <v>20</v>
+      </c>
+      <c r="C25" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E25" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="F25" s="13" t="s">
+      <c r="E25" s="5">
+        <v>2</v>
+      </c>
+      <c r="F25" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="H25" s="11">
-        <f t="shared" si="1"/>
+      <c r="G25" s="5">
+        <v>4</v>
+      </c>
+      <c r="H25" s="53">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26">
-      <c r="B26" s="7">
-        <v>21.0</v>
-      </c>
-      <c r="C26" s="10" t="s">
+    <row r="26" spans="2:11" ht="13.8">
+      <c r="B26" s="6">
+        <v>21</v>
+      </c>
+      <c r="C26" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="E26" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="H26" s="11">
-        <f t="shared" si="1"/>
+      <c r="E26" s="4">
+        <v>3</v>
+      </c>
+      <c r="F26" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="4">
+        <v>3</v>
+      </c>
+      <c r="H26" s="53">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27">
-      <c r="B27" s="7">
-        <v>22.0</v>
-      </c>
-      <c r="C27" s="12" t="s">
+    <row r="27" spans="2:11" ht="13.8">
+      <c r="B27" s="6">
+        <v>22</v>
+      </c>
+      <c r="C27" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="F27" s="13" t="s">
+      <c r="E27" s="5">
+        <v>2</v>
+      </c>
+      <c r="F27" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G27" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="H27" s="11">
-        <f t="shared" si="1"/>
+      <c r="G27" s="5">
+        <v>4</v>
+      </c>
+      <c r="H27" s="53">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28">
-      <c r="B28" s="7">
-        <v>23.0</v>
-      </c>
-      <c r="C28" s="8" t="s">
+    <row r="28" spans="2:11" ht="13.8">
+      <c r="B28" s="6">
+        <v>23</v>
+      </c>
+      <c r="C28" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="F28" s="9" t="s">
+      <c r="E28" s="4">
+        <v>3</v>
+      </c>
+      <c r="F28" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="9">
-        <v>5.0</v>
-      </c>
-      <c r="H28" s="11">
-        <f t="shared" si="1"/>
+      <c r="G28" s="4">
+        <v>5</v>
+      </c>
+      <c r="H28" s="52">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29">
-      <c r="B29" s="7">
-        <v>24.0</v>
-      </c>
-      <c r="C29" s="12" t="s">
+    <row r="29" spans="2:11" ht="13.8">
+      <c r="B29" s="6">
+        <v>24</v>
+      </c>
+      <c r="C29" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E29" s="13">
-        <v>5.0</v>
-      </c>
-      <c r="F29" s="13" t="s">
+      <c r="E29" s="5">
+        <v>5</v>
+      </c>
+      <c r="F29" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="G29" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="H29" s="11">
-        <f t="shared" si="1"/>
+      <c r="G29" s="5">
+        <v>1</v>
+      </c>
+      <c r="H29" s="53">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30">
-      <c r="B30" s="7">
-        <v>25.0</v>
-      </c>
-      <c r="C30" s="10" t="s">
+    <row r="30" spans="2:11" ht="13.8">
+      <c r="B30" s="6">
+        <v>25</v>
+      </c>
+      <c r="C30" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="E30" s="9">
-        <v>5.0</v>
-      </c>
-      <c r="F30" s="9" t="s">
+      <c r="E30" s="4">
+        <v>5</v>
+      </c>
+      <c r="F30" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="G30" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="H30" s="11">
-        <f t="shared" si="1"/>
+      <c r="G30" s="4">
+        <v>1</v>
+      </c>
+      <c r="H30" s="53">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31">
-      <c r="B31" s="7">
-        <v>26.0</v>
-      </c>
-      <c r="C31" s="13" t="s">
+    <row r="31" spans="2:11" ht="13.8">
+      <c r="B31" s="6">
+        <v>26</v>
+      </c>
+      <c r="C31" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="F31" s="13" t="s">
+      <c r="E31" s="5">
+        <v>3</v>
+      </c>
+      <c r="F31" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="G31" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="H31" s="11">
-        <f t="shared" si="1"/>
+      <c r="G31" s="5">
+        <v>3</v>
+      </c>
+      <c r="H31" s="53">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32">
-      <c r="B32" s="7">
-        <v>27.0</v>
-      </c>
-      <c r="C32" s="8" t="s">
+    <row r="32" spans="2:11" ht="13.8">
+      <c r="B32" s="6">
+        <v>27</v>
+      </c>
+      <c r="C32" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="9">
-        <v>4.0</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="H32" s="11">
-        <f t="shared" si="1"/>
+      <c r="E32" s="4">
+        <v>4</v>
+      </c>
+      <c r="F32" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="4">
+        <v>3</v>
+      </c>
+      <c r="H32" s="52">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33">
-      <c r="B33" s="7">
-        <v>28.0</v>
-      </c>
-      <c r="C33" s="12" t="s">
+    <row r="33" spans="2:11" ht="13.8">
+      <c r="B33" s="6">
+        <v>28</v>
+      </c>
+      <c r="C33" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E33" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G33" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="H33" s="11">
-        <f t="shared" si="1"/>
+      <c r="E33" s="5">
+        <v>3</v>
+      </c>
+      <c r="F33" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="5">
+        <v>3</v>
+      </c>
+      <c r="H33" s="53">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34">
-      <c r="B34" s="7">
-        <v>29.0</v>
-      </c>
-      <c r="C34" s="10" t="s">
+    <row r="34" spans="2:11" ht="13.8">
+      <c r="B34" s="6">
+        <v>29</v>
+      </c>
+      <c r="C34" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="E34" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="H34" s="11">
-        <f t="shared" si="1"/>
+      <c r="E34" s="4">
+        <v>3</v>
+      </c>
+      <c r="F34" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="4">
+        <v>3</v>
+      </c>
+      <c r="H34" s="53">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
     </row>
-    <row r="35">
-      <c r="B35" s="7">
-        <v>30.0</v>
-      </c>
-      <c r="C35" s="12" t="s">
+    <row r="35" spans="2:11" ht="13.8">
+      <c r="B35" s="6">
+        <v>30</v>
+      </c>
+      <c r="C35" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="F35" s="13" t="s">
+      <c r="E35" s="5">
+        <v>2</v>
+      </c>
+      <c r="F35" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G35" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="H35" s="11">
-        <f t="shared" si="1"/>
+      <c r="G35" s="5">
+        <v>4</v>
+      </c>
+      <c r="H35" s="53">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36">
-      <c r="B36" s="7">
-        <v>31.0</v>
-      </c>
-      <c r="C36" s="12" t="s">
+    <row r="36" spans="2:11" ht="13.8">
+      <c r="B36" s="6">
+        <v>31</v>
+      </c>
+      <c r="C36" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E36" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="F36" s="9" t="s">
+      <c r="E36" s="4">
+        <v>2</v>
+      </c>
+      <c r="F36" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G36" s="9">
-        <v>5.0</v>
-      </c>
-      <c r="H36" s="11">
-        <f t="shared" si="1"/>
+      <c r="G36" s="4">
+        <v>5</v>
+      </c>
+      <c r="H36" s="52">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37">
-      <c r="B37" s="7">
-        <v>32.0</v>
-      </c>
-      <c r="C37" s="14" t="s">
+    <row r="37" spans="2:11" ht="13.8">
+      <c r="B37" s="6">
+        <v>32</v>
+      </c>
+      <c r="C37" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E37" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="F37" s="13" t="s">
+      <c r="E37" s="5">
+        <v>3</v>
+      </c>
+      <c r="F37" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G37" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="H37" s="11">
-        <f t="shared" si="1"/>
+      <c r="G37" s="5">
+        <v>4</v>
+      </c>
+      <c r="H37" s="52">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38">
-      <c r="B38" s="7">
-        <v>33.0</v>
-      </c>
-      <c r="C38" s="8" t="s">
+    <row r="38" spans="2:11" ht="13.8">
+      <c r="B38" s="6">
+        <v>33</v>
+      </c>
+      <c r="C38" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="E38" s="9">
-        <v>5.0</v>
-      </c>
-      <c r="F38" s="10" t="s">
+      <c r="E38" s="4">
+        <v>5</v>
+      </c>
+      <c r="F38" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="G38" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="H38" s="11">
-        <f t="shared" si="1"/>
+      <c r="G38" s="4">
+        <v>2</v>
+      </c>
+      <c r="H38" s="52">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39">
-      <c r="B39" s="15">
-        <v>34.0</v>
-      </c>
-      <c r="C39" s="13" t="s">
+    <row r="39" spans="2:11" ht="13.8">
+      <c r="B39" s="7">
+        <v>34</v>
+      </c>
+      <c r="C39" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E39" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="F39" s="13" t="s">
+      <c r="E39" s="5">
+        <v>3</v>
+      </c>
+      <c r="F39" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="G39" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="H39" s="11">
-        <f t="shared" si="1"/>
+      <c r="G39" s="5">
+        <v>1</v>
+      </c>
+      <c r="H39" s="53">
+        <f>E39*G39</f>
         <v>3</v>
       </c>
       <c r="I39" s="2"/>
@@ -1498,6 +1719,7 @@
       <c r="K39" s="2"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/_ANALISIS DE RIESGOS.xlsx
+++ b/_ANALISIS DE RIESGOS.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Universidad\SEGUNDO\IS1\Proyecto-IS1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F22416-6BDA-44B7-8828-8F9AD7764DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="612" yWindow="588" windowWidth="21852" windowHeight="8676"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="67">
   <si>
     <t>RIESGO</t>
   </si>
@@ -212,13 +231,16 @@
   </si>
   <si>
     <t>Improbable</t>
+  </si>
+  <si>
+    <t>NOTA: Los riesgos que se analizarán en profundidad son los resaltados en amarillo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -271,8 +293,15 @@
       <color rgb="FF000000"/>
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -323,12 +352,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -384,6 +407,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
@@ -452,13 +487,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+  <cellXfs count="56">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -468,55 +503,59 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,12 +566,11 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -732,7 +770,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -749,8 +787,10 @@
     <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11">
-      <c r="C3" s="1"/>
+    <row r="3" spans="1:11" ht="13.2">
+      <c r="C3" s="55" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="13.8">
       <c r="C5" s="9" t="s">
@@ -794,8 +834,8 @@
       <c r="G6" s="4">
         <v>4</v>
       </c>
-      <c r="H6" s="52">
-        <f t="shared" ref="H6:H39" si="0">E6*G6</f>
+      <c r="H6" s="51">
+        <f t="shared" ref="H6:H38" si="0">E6*G6</f>
         <v>12</v>
       </c>
       <c r="I6" s="2"/>
@@ -810,7 +850,7 @@
       <c r="B7" s="6">
         <v>2</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="46" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="16" t="s">
@@ -825,7 +865,7 @@
       <c r="G7" s="5">
         <v>2</v>
       </c>
-      <c r="H7" s="53">
+      <c r="H7" s="52">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -841,7 +881,7 @@
       <c r="B8" s="6">
         <v>3</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="46" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="27" t="s">
@@ -856,7 +896,7 @@
       <c r="G8" s="4">
         <v>3</v>
       </c>
-      <c r="H8" s="53">
+      <c r="H8" s="52">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -887,7 +927,7 @@
       <c r="G9" s="5">
         <v>3</v>
       </c>
-      <c r="H9" s="52">
+      <c r="H9" s="51">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -918,7 +958,7 @@
       <c r="G10" s="4">
         <v>5</v>
       </c>
-      <c r="H10" s="52">
+      <c r="H10" s="51">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -949,7 +989,7 @@
       <c r="G11" s="5">
         <v>3</v>
       </c>
-      <c r="H11" s="52">
+      <c r="H11" s="51">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -965,7 +1005,7 @@
       <c r="B12" s="6">
         <v>7</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="47" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="32" t="s">
@@ -980,7 +1020,7 @@
       <c r="G12" s="4">
         <v>4</v>
       </c>
-      <c r="H12" s="53">
+      <c r="H12" s="52">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -992,7 +1032,7 @@
       <c r="B13" s="6">
         <v>8</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="48" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="28" t="s">
@@ -1007,7 +1047,7 @@
       <c r="G13" s="5">
         <v>3</v>
       </c>
-      <c r="H13" s="53">
+      <c r="H13" s="52">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1035,7 +1075,7 @@
       <c r="G14" s="4">
         <v>5</v>
       </c>
-      <c r="H14" s="52">
+      <c r="H14" s="51">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -1047,7 +1087,7 @@
       <c r="B15" s="6">
         <v>10</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="C15" s="49" t="s">
         <v>23</v>
       </c>
       <c r="D15" s="17" t="s">
@@ -1062,7 +1102,7 @@
       <c r="G15" s="5">
         <v>3</v>
       </c>
-      <c r="H15" s="53">
+      <c r="H15" s="52">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1074,7 +1114,7 @@
       <c r="B16" s="6">
         <v>11</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="47" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="18" t="s">
@@ -1089,7 +1129,7 @@
       <c r="G16" s="4">
         <v>2</v>
       </c>
-      <c r="H16" s="53">
+      <c r="H16" s="52">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1101,7 +1141,7 @@
       <c r="B17" s="6">
         <v>12</v>
       </c>
-      <c r="C17" s="49" t="s">
+      <c r="C17" s="48" t="s">
         <v>25</v>
       </c>
       <c r="D17" s="27" t="s">
@@ -1116,7 +1156,7 @@
       <c r="G17" s="5">
         <v>1</v>
       </c>
-      <c r="H17" s="53">
+      <c r="H17" s="52">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1128,7 +1168,7 @@
       <c r="B18" s="6">
         <v>13</v>
       </c>
-      <c r="C18" s="51" t="s">
+      <c r="C18" s="50" t="s">
         <v>27</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -1143,7 +1183,7 @@
       <c r="G18" s="4">
         <v>1</v>
       </c>
-      <c r="H18" s="53">
+      <c r="H18" s="52">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1170,7 +1210,7 @@
       <c r="G19" s="5">
         <v>3</v>
       </c>
-      <c r="H19" s="52">
+      <c r="H19" s="51">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1182,7 +1222,7 @@
       <c r="B20" s="6">
         <v>15</v>
       </c>
-      <c r="C20" s="48" t="s">
+      <c r="C20" s="47" t="s">
         <v>29</v>
       </c>
       <c r="D20" s="18" t="s">
@@ -1197,7 +1237,7 @@
       <c r="G20" s="4">
         <v>2</v>
       </c>
-      <c r="H20" s="53">
+      <c r="H20" s="52">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1224,7 +1264,7 @@
       <c r="G21" s="5">
         <v>5</v>
       </c>
-      <c r="H21" s="52">
+      <c r="H21" s="51">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1251,7 +1291,7 @@
       <c r="G22" s="4">
         <v>3</v>
       </c>
-      <c r="H22" s="52">
+      <c r="H22" s="51">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1263,7 +1303,7 @@
       <c r="B23" s="6">
         <v>18</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="48" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="17" t="s">
@@ -1278,7 +1318,7 @@
       <c r="G23" s="5">
         <v>3</v>
       </c>
-      <c r="H23" s="53">
+      <c r="H23" s="52">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1290,7 +1330,7 @@
       <c r="B24" s="6">
         <v>19</v>
       </c>
-      <c r="C24" s="48" t="s">
+      <c r="C24" s="47" t="s">
         <v>35</v>
       </c>
       <c r="D24" s="31" t="s">
@@ -1305,7 +1345,7 @@
       <c r="G24" s="4">
         <v>4</v>
       </c>
-      <c r="H24" s="53">
+      <c r="H24" s="52">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1317,7 +1357,7 @@
       <c r="B25" s="6">
         <v>20</v>
       </c>
-      <c r="C25" s="49" t="s">
+      <c r="C25" s="48" t="s">
         <v>37</v>
       </c>
       <c r="D25" s="29" t="s">
@@ -1332,7 +1372,7 @@
       <c r="G25" s="5">
         <v>4</v>
       </c>
-      <c r="H25" s="53">
+      <c r="H25" s="52">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1344,7 +1384,7 @@
       <c r="B26" s="6">
         <v>21</v>
       </c>
-      <c r="C26" s="48" t="s">
+      <c r="C26" s="47" t="s">
         <v>38</v>
       </c>
       <c r="D26" s="18" t="s">
@@ -1359,7 +1399,7 @@
       <c r="G26" s="4">
         <v>3</v>
       </c>
-      <c r="H26" s="53">
+      <c r="H26" s="52">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1371,7 +1411,7 @@
       <c r="B27" s="6">
         <v>22</v>
       </c>
-      <c r="C27" s="49" t="s">
+      <c r="C27" s="48" t="s">
         <v>39</v>
       </c>
       <c r="D27" s="29" t="s">
@@ -1386,7 +1426,7 @@
       <c r="G27" s="5">
         <v>4</v>
       </c>
-      <c r="H27" s="53">
+      <c r="H27" s="52">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1413,7 +1453,7 @@
       <c r="G28" s="4">
         <v>5</v>
       </c>
-      <c r="H28" s="52">
+      <c r="H28" s="51">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1425,7 +1465,7 @@
       <c r="B29" s="6">
         <v>24</v>
       </c>
-      <c r="C29" s="49" t="s">
+      <c r="C29" s="48" t="s">
         <v>41</v>
       </c>
       <c r="D29" s="21" t="s">
@@ -1440,7 +1480,7 @@
       <c r="G29" s="5">
         <v>1</v>
       </c>
-      <c r="H29" s="53">
+      <c r="H29" s="52">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1452,7 +1492,7 @@
       <c r="B30" s="6">
         <v>25</v>
       </c>
-      <c r="C30" s="48" t="s">
+      <c r="C30" s="47" t="s">
         <v>43</v>
       </c>
       <c r="D30" s="20" t="s">
@@ -1467,7 +1507,7 @@
       <c r="G30" s="4">
         <v>1</v>
       </c>
-      <c r="H30" s="53">
+      <c r="H30" s="52">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1479,7 +1519,7 @@
       <c r="B31" s="6">
         <v>26</v>
       </c>
-      <c r="C31" s="50" t="s">
+      <c r="C31" s="49" t="s">
         <v>44</v>
       </c>
       <c r="D31" s="17" t="s">
@@ -1494,7 +1534,7 @@
       <c r="G31" s="5">
         <v>3</v>
       </c>
-      <c r="H31" s="53">
+      <c r="H31" s="52">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1521,7 +1561,7 @@
       <c r="G32" s="4">
         <v>3</v>
       </c>
-      <c r="H32" s="52">
+      <c r="H32" s="51">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1533,7 +1573,7 @@
       <c r="B33" s="6">
         <v>28</v>
       </c>
-      <c r="C33" s="49" t="s">
+      <c r="C33" s="48" t="s">
         <v>49</v>
       </c>
       <c r="D33" s="17" t="s">
@@ -1548,7 +1588,7 @@
       <c r="G33" s="5">
         <v>3</v>
       </c>
-      <c r="H33" s="53">
+      <c r="H33" s="52">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1560,7 +1600,7 @@
       <c r="B34" s="6">
         <v>29</v>
       </c>
-      <c r="C34" s="48" t="s">
+      <c r="C34" s="47" t="s">
         <v>50</v>
       </c>
       <c r="D34" s="18" t="s">
@@ -1575,7 +1615,7 @@
       <c r="G34" s="4">
         <v>3</v>
       </c>
-      <c r="H34" s="53">
+      <c r="H34" s="52">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1587,7 +1627,7 @@
       <c r="B35" s="6">
         <v>30</v>
       </c>
-      <c r="C35" s="48" t="s">
+      <c r="C35" s="47" t="s">
         <v>51</v>
       </c>
       <c r="D35" s="29" t="s">
@@ -1602,7 +1642,7 @@
       <c r="G35" s="5">
         <v>4</v>
       </c>
-      <c r="H35" s="53">
+      <c r="H35" s="52">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1614,7 +1654,7 @@
       <c r="B36" s="6">
         <v>31</v>
       </c>
-      <c r="C36" s="45" t="s">
+      <c r="C36" s="53" t="s">
         <v>52</v>
       </c>
       <c r="D36" s="30" t="s">
@@ -1629,7 +1669,7 @@
       <c r="G36" s="4">
         <v>5</v>
       </c>
-      <c r="H36" s="52">
+      <c r="H36" s="54">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1641,7 +1681,7 @@
       <c r="B37" s="6">
         <v>32</v>
       </c>
-      <c r="C37" s="46" t="s">
+      <c r="C37" s="45" t="s">
         <v>53</v>
       </c>
       <c r="D37" s="17" t="s">
@@ -1656,7 +1696,7 @@
       <c r="G37" s="5">
         <v>4</v>
       </c>
-      <c r="H37" s="52">
+      <c r="H37" s="51">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1683,7 +1723,7 @@
       <c r="G38" s="4">
         <v>2</v>
       </c>
-      <c r="H38" s="52">
+      <c r="H38" s="51">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1695,7 +1735,7 @@
       <c r="B39" s="7">
         <v>34</v>
       </c>
-      <c r="C39" s="50" t="s">
+      <c r="C39" s="49" t="s">
         <v>55</v>
       </c>
       <c r="D39" s="17" t="s">
@@ -1710,7 +1750,7 @@
       <c r="G39" s="5">
         <v>1</v>
       </c>
-      <c r="H39" s="53">
+      <c r="H39" s="52">
         <f>E39*G39</f>
         <v>3</v>
       </c>

--- a/_ANALISIS DE RIESGOS.xlsx
+++ b/_ANALISIS DE RIESGOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Universidad\SEGUNDO\IS1\Proyecto-IS1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9999b953125d8be8/Desktop/TALLER/Proyecto-IS1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F22416-6BDA-44B7-8828-8F9AD7764DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{C1F22416-6BDA-44B7-8828-8F9AD7764DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31A06F79-42C1-4C9D-A744-0B8D99744A9C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="53">
   <si>
     <t>RIESGO</t>
   </si>
@@ -50,138 +50,9 @@
     <t>IMPORTANCIA DEL RIESGO</t>
   </si>
   <si>
-    <t>insuficiente espacio en la RAM</t>
-  </si>
-  <si>
-    <t>serio</t>
-  </si>
-  <si>
-    <t>probable</t>
-  </si>
-  <si>
-    <t>que funcione en todos nuestros ordenadores</t>
-  </si>
-  <si>
-    <t>remota</t>
-  </si>
-  <si>
-    <t>gestión del github (personas trabajando a la vez, que alguien no haga push, que alguien no haga pull y trabaje)</t>
-  </si>
-  <si>
-    <t>menor</t>
-  </si>
-  <si>
-    <t>ocasional</t>
-  </si>
-  <si>
-    <t>problemas con la migración de base de datos</t>
-  </si>
-  <si>
-    <t>crítica</t>
-  </si>
-  <si>
-    <t>delegar demasiado en la IA</t>
-  </si>
-  <si>
-    <t>frecuente</t>
-  </si>
-  <si>
-    <t>error en la conexión del backend y frontend</t>
-  </si>
-  <si>
-    <t>catastrófica</t>
-  </si>
-  <si>
-    <t>equivocación de los usuarios con los datos</t>
-  </si>
-  <si>
-    <t>insignificante</t>
-  </si>
-  <si>
-    <t>no llegar a la fecha semanal</t>
-  </si>
-  <si>
-    <t>falta de comunicación entre los miembros del equipo</t>
-  </si>
-  <si>
-    <t>no disponibilidad de los miembros</t>
-  </si>
-  <si>
-    <t>perder la contraseña del github</t>
-  </si>
-  <si>
-    <t>huelga muy larga</t>
-  </si>
-  <si>
-    <t>improbable</t>
-  </si>
-  <si>
-    <t>que se vaya la luz por un tiempo significante</t>
-  </si>
-  <si>
-    <t>fundirnos el presupuesto de IT al principio</t>
-  </si>
-  <si>
-    <t>enfermedades el dia de la presentación</t>
-  </si>
-  <si>
-    <t>seria</t>
-  </si>
-  <si>
-    <t>que se nos olvide el ordenador para trabajar en clase</t>
-  </si>
-  <si>
-    <t>problemas en el código de otros compañeros</t>
-  </si>
-  <si>
-    <t>critico</t>
-  </si>
-  <si>
-    <t>hacer mal historias de usuarios</t>
-  </si>
-  <si>
-    <t>hacer mal gestión de riesgos</t>
-  </si>
-  <si>
-    <t>insignifante</t>
-  </si>
-  <si>
-    <t>no emplear bien técnicas de scrum</t>
-  </si>
-  <si>
-    <t>equivocarse en el enfoque del proyecto</t>
-  </si>
-  <si>
-    <t>dedicar demasiado tiempo a partes no tan relevantes</t>
-  </si>
-  <si>
-    <t>desconocimiento (tecnologías, scrum, gestión de proyecto)</t>
-  </si>
-  <si>
-    <t>que nos hackeen el código</t>
-  </si>
-  <si>
-    <t>catastrofico</t>
-  </si>
-  <si>
-    <t>que nos roben los ordenadores</t>
-  </si>
-  <si>
-    <t>planificaciones incorrectas y  demasiado ambiciosas</t>
-  </si>
-  <si>
-    <t>Serio</t>
-  </si>
-  <si>
     <t>Ocasional</t>
   </si>
   <si>
-    <t>fallos en el código de la IA</t>
-  </si>
-  <si>
-    <t>Critico</t>
-  </si>
-  <si>
     <t>desarrollo erróneo de la interfaz de usuario</t>
   </si>
   <si>
@@ -209,9 +80,6 @@
     <t>Catastrófica</t>
   </si>
   <si>
-    <t>Crítico</t>
-  </si>
-  <si>
     <t>Menor</t>
   </si>
   <si>
@@ -234,13 +102,103 @@
   </si>
   <si>
     <t>NOTA: Los riesgos que se analizarán en profundidad son los resaltados en amarillo</t>
+  </si>
+  <si>
+    <t>NÚMERO</t>
+  </si>
+  <si>
+    <t>Quedarnos sin espacio en la RAM para la base de datos</t>
+  </si>
+  <si>
+    <t>Fallos de la aplicación en alguno de nuestros ordenadores</t>
+  </si>
+  <si>
+    <t>Tener una mala gestión del github (ej.: personas trabajando a la vez, no hacer push o pull,...)</t>
+  </si>
+  <si>
+    <t>Tener problemas con la migración de base de datos</t>
+  </si>
+  <si>
+    <t>Crítica</t>
+  </si>
+  <si>
+    <t>Seria</t>
+  </si>
+  <si>
+    <t>Delegar demasiado en la IA</t>
+  </si>
+  <si>
+    <t>Errores en la conexión del backend y frontend</t>
+  </si>
+  <si>
+    <t>Introducción de entradas y datos incorrectos</t>
+  </si>
+  <si>
+    <t>No acabafr los Sprints</t>
+  </si>
+  <si>
+    <t>Falta de comunicación entre los miembros del equipo</t>
+  </si>
+  <si>
+    <t>Indisponibilidad de los miembros</t>
+  </si>
+  <si>
+    <t>Perder la contraseña del github</t>
+  </si>
+  <si>
+    <t>Perder clases por muchas huelgas o de muy larga duración</t>
+  </si>
+  <si>
+    <t>No poder trabajar por que se vaya la luz por un tiempo significante</t>
+  </si>
+  <si>
+    <t>Fundir el presupuesto de IT demasiado pronto</t>
+  </si>
+  <si>
+    <t>Estar enfermos el día de la presentación</t>
+  </si>
+  <si>
+    <t>No tener el ordenador cuando haya que trabajar en clase</t>
+  </si>
+  <si>
+    <t>No hacer correctamente las historias de usuarios</t>
+  </si>
+  <si>
+    <t>No hacer correctamente la gestión de riesgos</t>
+  </si>
+  <si>
+    <t>Emplear incorrectamente las técnicas de scrum</t>
+  </si>
+  <si>
+    <t>Equivocarnos en el enfoque del proyecto</t>
+  </si>
+  <si>
+    <t>Dedicar demasiado tiempo a aspectos no tan relevantes</t>
+  </si>
+  <si>
+    <t>Desconocimiento en tecnologías, técnicas de scrum, gestión de proyecto,...</t>
+  </si>
+  <si>
+    <t>Que nos hackeen el código</t>
+  </si>
+  <si>
+    <t>Que nos roben los ordenadores</t>
+  </si>
+  <si>
+    <t>Realizar planificaciones incoherentes o demasiado ambiciosas</t>
+  </si>
+  <si>
+    <t>Fallos en el código de la IA</t>
+  </si>
+  <si>
+    <t>Errores o problemas en el código que suba otro compañero</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -300,6 +258,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="21">
     <fill>
@@ -423,7 +395,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -472,22 +444,37 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -500,15 +487,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -518,33 +498,25 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -556,6 +528,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -775,252 +759,255 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A3:K39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="101.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="101.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" ht="13.2">
-      <c r="C3" s="55" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="13.8">
-      <c r="C5" s="9" t="s">
+    <row r="3" spans="1:11" ht="12.75">
+      <c r="C3" s="42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15">
+      <c r="B5" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="9" t="s">
+      <c r="F5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>4</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" ht="13.8">
-      <c r="B6" s="8">
+    <row r="6" spans="1:11" ht="15">
+      <c r="B6" s="6">
         <v>1</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>6</v>
+      <c r="C6" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="E6" s="4">
         <v>3</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>7</v>
+      <c r="F6" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="G6" s="4">
         <v>4</v>
       </c>
-      <c r="H6" s="51">
+      <c r="H6" s="38">
         <f t="shared" ref="H6:H38" si="0">E6*G6</f>
         <v>12</v>
       </c>
       <c r="I6" s="2"/>
-      <c r="J6" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="13.8">
+      <c r="J6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="14.25">
       <c r="B7" s="6">
         <v>2</v>
       </c>
-      <c r="C7" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>6</v>
+      <c r="C7" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
       </c>
-      <c r="F7" s="34" t="s">
-        <v>9</v>
+      <c r="F7" s="27" t="s">
+        <v>20</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7" s="39">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="I7" s="2"/>
-      <c r="J7" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="13.8">
+      <c r="J7" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="14.25">
       <c r="B8" s="6">
         <v>3</v>
       </c>
-      <c r="C8" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>11</v>
+      <c r="C8" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>15</v>
       </c>
       <c r="E8" s="4">
         <v>2</v>
       </c>
-      <c r="F8" s="37" t="s">
-        <v>12</v>
+      <c r="F8" s="28" t="s">
+        <v>5</v>
       </c>
       <c r="G8" s="4">
         <v>3</v>
       </c>
-      <c r="H8" s="52">
+      <c r="H8" s="39">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="I8" s="2"/>
-      <c r="J8" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="K8" s="23" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="13.8">
+      <c r="J8" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15">
       <c r="B9" s="6">
         <v>4</v>
       </c>
-      <c r="C9" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>14</v>
+      <c r="C9" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>28</v>
       </c>
       <c r="E9" s="5">
         <v>4</v>
       </c>
-      <c r="F9" s="38" t="s">
+      <c r="F9" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="5">
+        <v>3</v>
+      </c>
+      <c r="H9" s="38">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="G9" s="5">
-        <v>3</v>
-      </c>
-      <c r="H9" s="51">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
       <c r="I9" s="2"/>
-      <c r="J9" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="13.8">
+      <c r="J9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15">
       <c r="B10" s="6">
         <v>5</v>
       </c>
-      <c r="C10" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>14</v>
+      <c r="C10" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>28</v>
       </c>
       <c r="E10" s="4">
         <v>4</v>
       </c>
-      <c r="F10" s="41" t="s">
-        <v>16</v>
+      <c r="F10" s="31" t="s">
+        <v>18</v>
       </c>
       <c r="G10" s="4">
         <v>5</v>
       </c>
-      <c r="H10" s="51">
+      <c r="H10" s="38">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="I10" s="2"/>
-      <c r="J10" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="K10" s="28" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="13.8">
+      <c r="J10" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15">
       <c r="B11" s="6">
         <v>6</v>
       </c>
-      <c r="C11" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>18</v>
+      <c r="C11" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>14</v>
       </c>
       <c r="E11" s="5">
         <v>5</v>
       </c>
-      <c r="F11" s="38" t="s">
-        <v>12</v>
+      <c r="F11" s="29" t="s">
+        <v>5</v>
       </c>
       <c r="G11" s="5">
         <v>3</v>
       </c>
-      <c r="H11" s="51">
+      <c r="H11" s="38">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="I11" s="2"/>
-      <c r="J11" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="K11" s="32" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="13.8">
+      <c r="J11" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="14.25">
       <c r="B12" s="6">
         <v>7</v>
       </c>
-      <c r="C12" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>20</v>
+      <c r="C12" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>16</v>
       </c>
       <c r="E12" s="4">
         <v>1</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>7</v>
+      <c r="F12" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="G12" s="4">
         <v>4</v>
       </c>
-      <c r="H12" s="52">
+      <c r="H12" s="39">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1028,26 +1015,26 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" ht="13.8">
+    <row r="13" spans="1:11" ht="14.25">
       <c r="B13" s="6">
         <v>8</v>
       </c>
-      <c r="C13" s="48" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>11</v>
+      <c r="C13" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>15</v>
       </c>
       <c r="E13" s="5">
         <v>2</v>
       </c>
-      <c r="F13" s="38" t="s">
-        <v>12</v>
+      <c r="F13" s="29" t="s">
+        <v>5</v>
       </c>
       <c r="G13" s="5">
         <v>3</v>
       </c>
-      <c r="H13" s="52">
+      <c r="H13" s="39">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1055,27 +1042,27 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" ht="13.8">
+    <row r="14" spans="1:11" ht="15">
       <c r="A14" s="1"/>
       <c r="B14" s="6">
         <v>9</v>
       </c>
-      <c r="C14" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>14</v>
+      <c r="C14" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="E14" s="4">
         <v>4</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>16</v>
+      <c r="F14" s="46" t="s">
+        <v>18</v>
       </c>
       <c r="G14" s="4">
         <v>5</v>
       </c>
-      <c r="H14" s="51">
+      <c r="H14" s="38">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -1083,26 +1070,26 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" ht="13.8">
+    <row r="15" spans="1:11" ht="14.25">
       <c r="B15" s="6">
         <v>10</v>
       </c>
-      <c r="C15" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>6</v>
+      <c r="C15" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="E15" s="5">
         <v>3</v>
       </c>
-      <c r="F15" s="39" t="s">
-        <v>12</v>
+      <c r="F15" s="47" t="s">
+        <v>5</v>
       </c>
       <c r="G15" s="5">
         <v>3</v>
       </c>
-      <c r="H15" s="52">
+      <c r="H15" s="39">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1110,26 +1097,26 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" ht="13.8">
+    <row r="16" spans="1:11" ht="14.25">
       <c r="B16" s="6">
         <v>11</v>
       </c>
-      <c r="C16" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>6</v>
+      <c r="C16" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="E16" s="4">
         <v>3</v>
       </c>
-      <c r="F16" s="35" t="s">
-        <v>9</v>
+      <c r="F16" s="48" t="s">
+        <v>20</v>
       </c>
       <c r="G16" s="4">
         <v>2</v>
       </c>
-      <c r="H16" s="52">
+      <c r="H16" s="39">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1137,26 +1124,26 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="2:11" ht="13.8">
+    <row r="17" spans="2:11" ht="14.25">
       <c r="B17" s="6">
         <v>12</v>
       </c>
-      <c r="C17" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>11</v>
+      <c r="C17" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>15</v>
       </c>
       <c r="E17" s="5">
         <v>2</v>
       </c>
-      <c r="F17" s="42" t="s">
-        <v>26</v>
+      <c r="F17" s="49" t="s">
+        <v>21</v>
       </c>
       <c r="G17" s="5">
         <v>1</v>
       </c>
-      <c r="H17" s="52">
+      <c r="H17" s="39">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1164,26 +1151,26 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="2:11" ht="13.8">
+    <row r="18" spans="2:11" ht="14.25">
       <c r="B18" s="6">
         <v>13</v>
       </c>
-      <c r="C18" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>18</v>
+      <c r="C18" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>14</v>
       </c>
       <c r="E18" s="4">
         <v>5</v>
       </c>
-      <c r="F18" s="43" t="s">
-        <v>26</v>
+      <c r="F18" s="50" t="s">
+        <v>21</v>
       </c>
       <c r="G18" s="4">
         <v>1</v>
       </c>
-      <c r="H18" s="52">
+      <c r="H18" s="39">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1191,26 +1178,26 @@
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="2:11" ht="13.8">
+    <row r="19" spans="2:11" ht="15">
       <c r="B19" s="6">
         <v>14</v>
       </c>
-      <c r="C19" s="44" t="s">
+      <c r="C19" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="19" t="s">
         <v>28</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>14</v>
       </c>
       <c r="E19" s="5">
         <v>4</v>
       </c>
-      <c r="F19" s="39" t="s">
-        <v>12</v>
+      <c r="F19" s="28" t="s">
+        <v>5</v>
       </c>
       <c r="G19" s="5">
         <v>3</v>
       </c>
-      <c r="H19" s="51">
+      <c r="H19" s="38">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1218,26 +1205,26 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="2:11" ht="13.8">
+    <row r="20" spans="2:11" ht="14.25">
       <c r="B20" s="6">
         <v>15</v>
       </c>
-      <c r="C20" s="47" t="s">
+      <c r="C20" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="18" t="s">
-        <v>30</v>
-      </c>
       <c r="E20" s="4">
         <v>3</v>
       </c>
-      <c r="F20" s="35" t="s">
-        <v>9</v>
+      <c r="F20" s="27" t="s">
+        <v>20</v>
       </c>
       <c r="G20" s="4">
         <v>2</v>
       </c>
-      <c r="H20" s="52">
+      <c r="H20" s="39">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1245,26 +1232,26 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="2:11" ht="13.8">
+    <row r="21" spans="2:11" ht="15">
       <c r="B21" s="6">
         <v>16</v>
       </c>
-      <c r="C21" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>30</v>
+      <c r="C21" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="E21" s="5">
         <v>3</v>
       </c>
-      <c r="F21" s="11" t="s">
-        <v>16</v>
+      <c r="F21" s="31" t="s">
+        <v>18</v>
       </c>
       <c r="G21" s="5">
         <v>5</v>
       </c>
-      <c r="H21" s="51">
+      <c r="H21" s="38">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1272,26 +1259,26 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="2:11" ht="13.8">
+    <row r="22" spans="2:11" ht="15">
       <c r="B22" s="6">
         <v>17</v>
       </c>
-      <c r="C22" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>33</v>
+      <c r="C22" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>28</v>
       </c>
       <c r="E22" s="4">
         <v>4</v>
       </c>
-      <c r="F22" s="40" t="s">
-        <v>12</v>
+      <c r="F22" s="28" t="s">
+        <v>5</v>
       </c>
       <c r="G22" s="4">
         <v>3</v>
       </c>
-      <c r="H22" s="51">
+      <c r="H22" s="38">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1299,26 +1286,26 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="2:11" ht="13.8">
+    <row r="23" spans="2:11" ht="14.25">
       <c r="B23" s="6">
         <v>18</v>
       </c>
-      <c r="C23" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>6</v>
+      <c r="C23" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="E23" s="5">
         <v>3</v>
       </c>
-      <c r="F23" s="39" t="s">
-        <v>12</v>
+      <c r="F23" s="28" t="s">
+        <v>5</v>
       </c>
       <c r="G23" s="5">
         <v>3</v>
       </c>
-      <c r="H23" s="52">
+      <c r="H23" s="39">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1326,26 +1313,26 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="2:11" ht="13.8">
+    <row r="24" spans="2:11" ht="14.25">
       <c r="B24" s="6">
         <v>19</v>
       </c>
-      <c r="C24" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>36</v>
+      <c r="C24" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>16</v>
       </c>
       <c r="E24" s="4">
         <v>1</v>
       </c>
-      <c r="F24" s="13" t="s">
-        <v>7</v>
+      <c r="F24" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="G24" s="4">
         <v>4</v>
       </c>
-      <c r="H24" s="52">
+      <c r="H24" s="39">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1353,26 +1340,26 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="2:11" ht="13.8">
+    <row r="25" spans="2:11" ht="14.25">
       <c r="B25" s="6">
         <v>20</v>
       </c>
-      <c r="C25" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="29" t="s">
-        <v>11</v>
+      <c r="C25" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>15</v>
       </c>
       <c r="E25" s="5">
         <v>2</v>
       </c>
-      <c r="F25" s="14" t="s">
-        <v>7</v>
+      <c r="F25" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="G25" s="5">
         <v>4</v>
       </c>
-      <c r="H25" s="52">
+      <c r="H25" s="39">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1380,26 +1367,26 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="2:11" ht="13.8">
+    <row r="26" spans="2:11" ht="14.25">
       <c r="B26" s="6">
         <v>21</v>
       </c>
-      <c r="C26" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>6</v>
+      <c r="C26" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="E26" s="4">
         <v>3</v>
       </c>
-      <c r="F26" s="40" t="s">
-        <v>12</v>
+      <c r="F26" s="28" t="s">
+        <v>5</v>
       </c>
       <c r="G26" s="4">
         <v>3</v>
       </c>
-      <c r="H26" s="52">
+      <c r="H26" s="39">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1407,26 +1394,26 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="2:11" ht="13.8">
+    <row r="27" spans="2:11" ht="14.25">
       <c r="B27" s="6">
         <v>22</v>
       </c>
-      <c r="C27" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>11</v>
+      <c r="C27" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>15</v>
       </c>
       <c r="E27" s="5">
         <v>2</v>
       </c>
-      <c r="F27" s="14" t="s">
-        <v>7</v>
+      <c r="F27" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="G27" s="5">
         <v>4</v>
       </c>
-      <c r="H27" s="52">
+      <c r="H27" s="39">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1434,26 +1421,26 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="2:11" ht="13.8">
+    <row r="28" spans="2:11" ht="15">
       <c r="B28" s="6">
         <v>23</v>
       </c>
-      <c r="C28" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>6</v>
+      <c r="C28" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="E28" s="4">
         <v>3</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>16</v>
+      <c r="F28" s="31" t="s">
+        <v>18</v>
       </c>
       <c r="G28" s="4">
         <v>5</v>
       </c>
-      <c r="H28" s="51">
+      <c r="H28" s="38">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1461,26 +1448,26 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="2:11" ht="13.8">
+    <row r="29" spans="2:11" ht="14.25">
       <c r="B29" s="6">
         <v>24</v>
       </c>
-      <c r="C29" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>42</v>
+      <c r="C29" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>14</v>
       </c>
       <c r="E29" s="5">
         <v>5</v>
       </c>
-      <c r="F29" s="42" t="s">
-        <v>26</v>
+      <c r="F29" s="49" t="s">
+        <v>21</v>
       </c>
       <c r="G29" s="5">
         <v>1</v>
       </c>
-      <c r="H29" s="52">
+      <c r="H29" s="39">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1488,26 +1475,26 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="2:11" ht="13.8">
+    <row r="30" spans="2:11" ht="14.25">
       <c r="B30" s="6">
         <v>25</v>
       </c>
-      <c r="C30" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>42</v>
+      <c r="C30" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>14</v>
       </c>
       <c r="E30" s="4">
         <v>5</v>
       </c>
-      <c r="F30" s="43" t="s">
-        <v>26</v>
+      <c r="F30" s="49" t="s">
+        <v>21</v>
       </c>
       <c r="G30" s="4">
         <v>1</v>
       </c>
-      <c r="H30" s="52">
+      <c r="H30" s="39">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1515,26 +1502,26 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="2:11" ht="13.8">
+    <row r="31" spans="2:11" ht="14.25">
       <c r="B31" s="6">
         <v>26</v>
       </c>
-      <c r="C31" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>45</v>
+      <c r="C31" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="E31" s="5">
         <v>3</v>
       </c>
-      <c r="F31" s="39" t="s">
-        <v>46</v>
+      <c r="F31" s="30" t="s">
+        <v>5</v>
       </c>
       <c r="G31" s="5">
         <v>3</v>
       </c>
-      <c r="H31" s="52">
+      <c r="H31" s="39">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1542,26 +1529,26 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="2:11" ht="13.8">
+    <row r="32" spans="2:11" ht="15">
       <c r="B32" s="6">
         <v>27</v>
       </c>
-      <c r="C32" s="44" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>48</v>
+      <c r="C32" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>28</v>
       </c>
       <c r="E32" s="4">
         <v>4</v>
       </c>
-      <c r="F32" s="40" t="s">
-        <v>12</v>
+      <c r="F32" s="28" t="s">
+        <v>5</v>
       </c>
       <c r="G32" s="4">
         <v>3</v>
       </c>
-      <c r="H32" s="51">
+      <c r="H32" s="38">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1569,26 +1556,26 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="2:11" ht="13.8">
+    <row r="33" spans="2:11" ht="14.25">
       <c r="B33" s="6">
         <v>28</v>
       </c>
-      <c r="C33" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" s="17" t="s">
+      <c r="C33" s="36" t="s">
         <v>6</v>
       </c>
+      <c r="D33" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="E33" s="5">
         <v>3</v>
       </c>
-      <c r="F33" s="39" t="s">
-        <v>12</v>
+      <c r="F33" s="28" t="s">
+        <v>5</v>
       </c>
       <c r="G33" s="5">
         <v>3</v>
       </c>
-      <c r="H33" s="52">
+      <c r="H33" s="39">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1596,26 +1583,26 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="2:11" ht="13.8">
+    <row r="34" spans="2:11" ht="14.25">
       <c r="B34" s="6">
         <v>29</v>
       </c>
-      <c r="C34" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>6</v>
+      <c r="C34" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="E34" s="4">
         <v>3</v>
       </c>
-      <c r="F34" s="40" t="s">
-        <v>12</v>
+      <c r="F34" s="28" t="s">
+        <v>5</v>
       </c>
       <c r="G34" s="4">
         <v>3</v>
       </c>
-      <c r="H34" s="52">
+      <c r="H34" s="39">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1623,26 +1610,26 @@
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="2:11" ht="13.8">
+    <row r="35" spans="2:11" ht="14.25">
       <c r="B35" s="6">
         <v>30</v>
       </c>
-      <c r="C35" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="D35" s="29" t="s">
-        <v>11</v>
+      <c r="C35" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>15</v>
       </c>
       <c r="E35" s="5">
         <v>2</v>
       </c>
-      <c r="F35" s="14" t="s">
-        <v>7</v>
+      <c r="F35" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="G35" s="5">
         <v>4</v>
       </c>
-      <c r="H35" s="52">
+      <c r="H35" s="39">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1650,26 +1637,26 @@
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="2:11" ht="13.8">
+    <row r="36" spans="2:11" ht="14.25">
       <c r="B36" s="6">
         <v>31</v>
       </c>
-      <c r="C36" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" s="30" t="s">
-        <v>11</v>
+      <c r="C36" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>15</v>
       </c>
       <c r="E36" s="4">
         <v>2</v>
       </c>
-      <c r="F36" s="10" t="s">
-        <v>16</v>
+      <c r="F36" s="31" t="s">
+        <v>18</v>
       </c>
       <c r="G36" s="4">
         <v>5</v>
       </c>
-      <c r="H36" s="54">
+      <c r="H36" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1677,26 +1664,26 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="2:11" ht="13.8">
+    <row r="37" spans="2:11" ht="15">
       <c r="B37" s="6">
         <v>32</v>
       </c>
-      <c r="C37" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>6</v>
+      <c r="C37" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="E37" s="5">
         <v>3</v>
       </c>
-      <c r="F37" s="14" t="s">
-        <v>7</v>
+      <c r="F37" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="G37" s="5">
         <v>4</v>
       </c>
-      <c r="H37" s="51">
+      <c r="H37" s="38">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1704,26 +1691,26 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="2:11" ht="13.8">
+    <row r="38" spans="2:11" ht="15">
       <c r="B38" s="6">
         <v>33</v>
       </c>
-      <c r="C38" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="D38" s="22" t="s">
-        <v>18</v>
+      <c r="C38" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>14</v>
       </c>
       <c r="E38" s="4">
         <v>5</v>
       </c>
-      <c r="F38" s="36" t="s">
-        <v>9</v>
+      <c r="F38" s="27" t="s">
+        <v>20</v>
       </c>
       <c r="G38" s="4">
         <v>2</v>
       </c>
-      <c r="H38" s="51">
+      <c r="H38" s="38">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1731,26 +1718,26 @@
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="2:11" ht="13.8">
+    <row r="39" spans="2:11" ht="14.25">
       <c r="B39" s="7">
         <v>34</v>
       </c>
-      <c r="C39" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>6</v>
+      <c r="C39" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="E39" s="5">
         <v>3</v>
       </c>
-      <c r="F39" s="42" t="s">
-        <v>26</v>
+      <c r="F39" s="49" t="s">
+        <v>21</v>
       </c>
       <c r="G39" s="5">
         <v>1</v>
       </c>
-      <c r="H39" s="52">
+      <c r="H39" s="39">
         <f>E39*G39</f>
         <v>3</v>
       </c>

--- a/_ANALISIS DE RIESGOS.xlsx
+++ b/_ANALISIS DE RIESGOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9999b953125d8be8/Desktop/TALLER/Proyecto-IS1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{C1F22416-6BDA-44B7-8828-8F9AD7764DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31A06F79-42C1-4C9D-A744-0B8D99744A9C}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="13_ncr:1_{C1F22416-6BDA-44B7-8828-8F9AD7764DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FDB0FF9-B2E6-47CC-8BB5-1C8931A3ABB2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="62">
   <si>
     <t>RIESGO</t>
   </si>
@@ -53,27 +53,6 @@
     <t>Ocasional</t>
   </si>
   <si>
-    <t>desarrollo erróneo de la interfaz de usuario</t>
-  </si>
-  <si>
-    <t>continua corriente de cambios en los requisitos</t>
-  </si>
-  <si>
-    <t>deficiencias en componentes proporcionados externamente</t>
-  </si>
-  <si>
-    <t>deficiencias en rendimiento en tiempo real</t>
-  </si>
-  <si>
-    <t>no ser capaces de aprovechar el potencial de las distintas tecnologias</t>
-  </si>
-  <si>
-    <t>no llegar a la fecha final</t>
-  </si>
-  <si>
-    <t>pandemia repentina</t>
-  </si>
-  <si>
     <t>Repercusión</t>
   </si>
   <si>
@@ -134,9 +113,6 @@
     <t>Introducción de entradas y datos incorrectos</t>
   </si>
   <si>
-    <t>No acabafr los Sprints</t>
-  </si>
-  <si>
     <t>Falta de comunicación entre los miembros del equipo</t>
   </si>
   <si>
@@ -192,13 +168,64 @@
   </si>
   <si>
     <t>Errores o problemas en el código que suba otro compañero</t>
+  </si>
+  <si>
+    <t>Desarrollar erróneamente la interfaz de usuario</t>
+  </si>
+  <si>
+    <t>Cambios continuos en los requisitos del proyecto</t>
+  </si>
+  <si>
+    <t>Deficiencias en componentes proporcionados externamente</t>
+  </si>
+  <si>
+    <t>Deficiencias en rendimiento en tiempo real</t>
+  </si>
+  <si>
+    <t>Mal aprovechamiento del potencial de las distintas tecnologías</t>
+  </si>
+  <si>
+    <t>No acabar los Sprints</t>
+  </si>
+  <si>
+    <t>No acabar el proyecto para la entrega final</t>
+  </si>
+  <si>
+    <t>Pandemia repentina</t>
+  </si>
+  <si>
+    <t>|</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>INTOLERABLE</t>
+  </si>
+  <si>
+    <t>ALTA</t>
+  </si>
+  <si>
+    <t>MEDIA</t>
+  </si>
+  <si>
+    <t>BAJA</t>
+  </si>
+  <si>
+    <t>TOLERABLE</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>Intolerable</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -272,8 +299,22 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -394,8 +435,44 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -470,11 +547,132 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -512,11 +710,9 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -540,6 +736,60 @@
     <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -758,7 +1008,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A3:K39"/>
+  <dimension ref="A3:Q39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="101.28515625" bestFit="1" customWidth="1"/>
@@ -767,112 +1017,161 @@
     <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="34.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" ht="12.75">
-      <c r="C3" s="42" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15">
-      <c r="B5" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="44" t="s">
+    <row r="3" spans="1:17" ht="12.75">
+      <c r="C3" s="40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15">
+      <c r="B5" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="42" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="41" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:11" ht="15">
+      <c r="I5" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="58"/>
+      <c r="M5" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="56"/>
+    </row>
+    <row r="6" spans="1:17" ht="15">
       <c r="B6" s="6">
         <v>1</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E6" s="4">
         <v>3</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G6" s="4">
         <v>4</v>
       </c>
-      <c r="H6" s="38">
-        <f t="shared" ref="H6:H38" si="0">E6*G6</f>
+      <c r="H6" s="77" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="36">
+        <f t="shared" ref="I6:I38" si="0">E6*G6</f>
         <v>12</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="14.25">
+      <c r="J6" s="2"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="66" t="s">
+        <v>7</v>
+      </c>
+      <c r="N6" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q6" s="70" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="14.25" customHeight="1">
       <c r="B7" s="6">
         <v>2</v>
       </c>
-      <c r="C7" s="34" t="s">
-        <v>25</v>
+      <c r="C7" s="33" t="s">
+        <v>18</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
       </c>
-      <c r="H7" s="39">
+      <c r="H7" s="76" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="14.25">
+      <c r="J7" s="2"/>
+      <c r="K7" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="61" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="71" t="s">
+        <v>55</v>
+      </c>
+      <c r="N7" s="71" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="71" t="s">
+        <v>55</v>
+      </c>
+      <c r="P7" s="72" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q7" s="73" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="14.25" customHeight="1">
       <c r="B8" s="6">
         <v>3</v>
       </c>
-      <c r="C8" s="34" t="s">
-        <v>26</v>
+      <c r="C8" s="33" t="s">
+        <v>19</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E8" s="4">
         <v>2</v>
@@ -883,27 +1182,43 @@
       <c r="G8" s="4">
         <v>3</v>
       </c>
-      <c r="H8" s="39">
+      <c r="H8" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15">
+      <c r="J8" s="2"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="M8" s="71" t="s">
+        <v>55</v>
+      </c>
+      <c r="N8" s="71" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" s="72" t="s">
+        <v>56</v>
+      </c>
+      <c r="P8" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q8" s="74" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="15">
       <c r="B9" s="6">
         <v>4</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E9" s="5">
         <v>4</v>
@@ -914,116 +1229,165 @@
       <c r="G9" s="5">
         <v>3</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9" s="77" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="36">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15">
+      <c r="J9" s="2"/>
+      <c r="K9" s="53"/>
+      <c r="L9" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="72" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" s="72" t="s">
+        <v>56</v>
+      </c>
+      <c r="O9" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="P9" s="74" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q9" s="75" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="15">
       <c r="B10" s="6">
         <v>5</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E10" s="4">
         <v>4</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G10" s="4">
         <v>5</v>
       </c>
-      <c r="H10" s="38">
+      <c r="H10" s="78" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" s="36">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15">
+      <c r="J10" s="2"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="M10" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="O10" s="74" t="s">
+        <v>58</v>
+      </c>
+      <c r="P10" s="75" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q10" s="75" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="15">
       <c r="B11" s="6">
         <v>6</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D11" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="5">
+        <v>5</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="5">
+        <v>3</v>
+      </c>
+      <c r="H11" s="77" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="36">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="5">
-        <v>5</v>
-      </c>
-      <c r="F11" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="G11" s="5">
-        <v>3</v>
-      </c>
-      <c r="H11" s="38">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11" s="25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="14.25">
+      <c r="M11" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="N11" s="74" t="s">
+        <v>58</v>
+      </c>
+      <c r="O11" s="75" t="s">
+        <v>59</v>
+      </c>
+      <c r="P11" s="75" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q11" s="75" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="14.25">
       <c r="B12" s="6">
         <v>7</v>
       </c>
-      <c r="C12" s="35" t="s">
-        <v>32</v>
+      <c r="C12" s="34" t="s">
+        <v>25</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E12" s="4">
         <v>1</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G12" s="4">
         <v>4</v>
       </c>
-      <c r="H12" s="39">
+      <c r="H12" s="4"/>
+      <c r="I12" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" ht="14.25">
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:17" ht="14.25">
       <c r="B13" s="6">
         <v>8</v>
       </c>
-      <c r="C13" s="36" t="s">
-        <v>33</v>
+      <c r="C13" s="35" t="s">
+        <v>50</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E13" s="5">
         <v>2</v>
@@ -1034,159 +1398,165 @@
       <c r="G13" s="5">
         <v>3</v>
       </c>
-      <c r="H13" s="39">
+      <c r="H13" s="5"/>
+      <c r="I13" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" ht="15">
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:17" ht="15">
       <c r="A14" s="1"/>
       <c r="B14" s="6">
         <v>9</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E14" s="4">
         <v>4</v>
       </c>
-      <c r="F14" s="46" t="s">
-        <v>18</v>
+      <c r="F14" s="44" t="s">
+        <v>11</v>
       </c>
       <c r="G14" s="4">
         <v>5</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14" s="4"/>
+      <c r="I14" s="36">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" ht="14.25">
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:17" ht="14.25">
       <c r="B15" s="6">
         <v>10</v>
       </c>
-      <c r="C15" s="51" t="s">
-        <v>35</v>
+      <c r="C15" s="49" t="s">
+        <v>27</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E15" s="5">
         <v>3</v>
       </c>
-      <c r="F15" s="47" t="s">
+      <c r="F15" s="45" t="s">
         <v>5</v>
       </c>
       <c r="G15" s="5">
         <v>3</v>
       </c>
-      <c r="H15" s="39">
+      <c r="H15" s="5"/>
+      <c r="I15" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" ht="14.25">
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:17" ht="14.25">
       <c r="B16" s="6">
         <v>11</v>
       </c>
-      <c r="C16" s="35" t="s">
-        <v>36</v>
+      <c r="C16" s="34" t="s">
+        <v>28</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E16" s="4">
         <v>3</v>
       </c>
-      <c r="F16" s="48" t="s">
-        <v>20</v>
+      <c r="F16" s="46" t="s">
+        <v>13</v>
       </c>
       <c r="G16" s="4">
         <v>2</v>
       </c>
-      <c r="H16" s="39">
+      <c r="H16" s="4"/>
+      <c r="I16" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="2:11" ht="14.25">
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="2:12" ht="14.25">
       <c r="B17" s="6">
         <v>12</v>
       </c>
-      <c r="C17" s="36" t="s">
-        <v>37</v>
+      <c r="C17" s="35" t="s">
+        <v>29</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E17" s="5">
         <v>2</v>
       </c>
-      <c r="F17" s="49" t="s">
-        <v>21</v>
+      <c r="F17" s="47" t="s">
+        <v>14</v>
       </c>
       <c r="G17" s="5">
         <v>1</v>
       </c>
-      <c r="H17" s="39">
+      <c r="H17" s="5"/>
+      <c r="I17" s="37">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="2:11" ht="14.25">
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="2:12" ht="14.25">
       <c r="B18" s="6">
         <v>13</v>
       </c>
-      <c r="C18" s="52" t="s">
-        <v>38</v>
+      <c r="C18" s="50" t="s">
+        <v>30</v>
       </c>
       <c r="D18" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="4">
+        <v>5</v>
+      </c>
+      <c r="F18" s="48" t="s">
         <v>14</v>
-      </c>
-      <c r="E18" s="4">
-        <v>5</v>
-      </c>
-      <c r="F18" s="50" t="s">
-        <v>21</v>
       </c>
       <c r="G18" s="4">
         <v>1</v>
       </c>
-      <c r="H18" s="39">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="I18" s="2"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="37">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="2:11" ht="15">
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="2:12" ht="15">
       <c r="B19" s="6">
         <v>14</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E19" s="5">
         <v>4</v>
@@ -1197,77 +1567,80 @@
       <c r="G19" s="5">
         <v>3</v>
       </c>
-      <c r="H19" s="38">
+      <c r="H19" s="5"/>
+      <c r="I19" s="36">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="2:11" ht="14.25">
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" spans="2:12" ht="14.25">
       <c r="B20" s="6">
         <v>15</v>
       </c>
-      <c r="C20" s="35" t="s">
-        <v>40</v>
+      <c r="C20" s="34" t="s">
+        <v>32</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E20" s="4">
         <v>3</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G20" s="4">
         <v>2</v>
       </c>
-      <c r="H20" s="39">
+      <c r="H20" s="4"/>
+      <c r="I20" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="2:11" ht="15">
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="2:12" ht="15">
       <c r="B21" s="6">
         <v>16</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E21" s="5">
         <v>3</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G21" s="5">
         <v>5</v>
       </c>
-      <c r="H21" s="38">
+      <c r="H21" s="5"/>
+      <c r="I21" s="36">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="2:11" ht="15">
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" spans="2:12" ht="15">
       <c r="B22" s="6">
         <v>17</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E22" s="4">
         <v>4</v>
@@ -1278,23 +1651,24 @@
       <c r="G22" s="4">
         <v>3</v>
       </c>
-      <c r="H22" s="38">
+      <c r="H22" s="4"/>
+      <c r="I22" s="36">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="2:11" ht="14.25">
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" spans="2:12" ht="14.25">
       <c r="B23" s="6">
         <v>18</v>
       </c>
-      <c r="C23" s="36" t="s">
-        <v>42</v>
+      <c r="C23" s="35" t="s">
+        <v>34</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E23" s="5">
         <v>3</v>
@@ -1305,77 +1679,80 @@
       <c r="G23" s="5">
         <v>3</v>
       </c>
-      <c r="H23" s="39">
+      <c r="H23" s="5"/>
+      <c r="I23" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="2:11" ht="14.25">
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" spans="2:12" ht="14.25">
       <c r="B24" s="6">
         <v>19</v>
       </c>
-      <c r="C24" s="35" t="s">
-        <v>43</v>
+      <c r="C24" s="34" t="s">
+        <v>35</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E24" s="4">
         <v>1</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G24" s="4">
         <v>4</v>
       </c>
-      <c r="H24" s="39">
+      <c r="H24" s="4"/>
+      <c r="I24" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="2:11" ht="14.25">
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" spans="2:12" ht="14.25">
       <c r="B25" s="6">
         <v>20</v>
       </c>
-      <c r="C25" s="36" t="s">
-        <v>44</v>
+      <c r="C25" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E25" s="5">
         <v>2</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G25" s="5">
         <v>4</v>
       </c>
-      <c r="H25" s="39">
+      <c r="H25" s="5"/>
+      <c r="I25" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="2:11" ht="14.25">
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" spans="2:12" ht="14.25">
       <c r="B26" s="6">
         <v>21</v>
       </c>
-      <c r="C26" s="35" t="s">
-        <v>45</v>
+      <c r="C26" s="34" t="s">
+        <v>37</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E26" s="4">
         <v>3</v>
@@ -1386,131 +1763,136 @@
       <c r="G26" s="4">
         <v>3</v>
       </c>
-      <c r="H26" s="39">
+      <c r="H26" s="4"/>
+      <c r="I26" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="2:11" ht="14.25">
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" spans="2:12" ht="14.25">
       <c r="B27" s="6">
         <v>22</v>
       </c>
-      <c r="C27" s="36" t="s">
-        <v>46</v>
+      <c r="C27" s="35" t="s">
+        <v>38</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E27" s="5">
         <v>2</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G27" s="5">
         <v>4</v>
       </c>
-      <c r="H27" s="39">
+      <c r="H27" s="5"/>
+      <c r="I27" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="2:11" ht="15">
+      <c r="L27" s="2"/>
+    </row>
+    <row r="28" spans="2:12" ht="15">
       <c r="B28" s="6">
         <v>23</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E28" s="4">
         <v>3</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G28" s="4">
         <v>5</v>
       </c>
-      <c r="H28" s="38">
+      <c r="H28" s="4"/>
+      <c r="I28" s="36">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="2:11" ht="14.25">
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" spans="2:12" ht="14.25">
       <c r="B29" s="6">
         <v>24</v>
       </c>
-      <c r="C29" s="36" t="s">
-        <v>48</v>
+      <c r="C29" s="35" t="s">
+        <v>40</v>
       </c>
       <c r="D29" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="5">
+        <v>5</v>
+      </c>
+      <c r="F29" s="47" t="s">
         <v>14</v>
-      </c>
-      <c r="E29" s="5">
-        <v>5</v>
-      </c>
-      <c r="F29" s="49" t="s">
-        <v>21</v>
       </c>
       <c r="G29" s="5">
         <v>1</v>
       </c>
-      <c r="H29" s="39">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="I29" s="2"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="37">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="2:11" ht="14.25">
+      <c r="L29" s="2"/>
+    </row>
+    <row r="30" spans="2:12" ht="14.25">
       <c r="B30" s="6">
         <v>25</v>
       </c>
-      <c r="C30" s="35" t="s">
-        <v>49</v>
+      <c r="C30" s="34" t="s">
+        <v>41</v>
       </c>
       <c r="D30" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="4">
+        <v>5</v>
+      </c>
+      <c r="F30" s="47" t="s">
         <v>14</v>
-      </c>
-      <c r="E30" s="4">
-        <v>5</v>
-      </c>
-      <c r="F30" s="49" t="s">
-        <v>21</v>
       </c>
       <c r="G30" s="4">
         <v>1</v>
       </c>
-      <c r="H30" s="39">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="I30" s="2"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="37">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="2:11" ht="14.25">
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" spans="2:12" ht="14.25">
       <c r="B31" s="6">
         <v>26</v>
       </c>
-      <c r="C31" s="51" t="s">
-        <v>50</v>
+      <c r="C31" s="49" t="s">
+        <v>42</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E31" s="5">
         <v>3</v>
@@ -1521,23 +1903,24 @@
       <c r="G31" s="5">
         <v>3</v>
       </c>
-      <c r="H31" s="39">
+      <c r="H31" s="5"/>
+      <c r="I31" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="2:11" ht="15">
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" spans="2:12" ht="15">
       <c r="B32" s="6">
         <v>27</v>
       </c>
       <c r="C32" s="32" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E32" s="4">
         <v>4</v>
@@ -1548,23 +1931,24 @@
       <c r="G32" s="4">
         <v>3</v>
       </c>
-      <c r="H32" s="38">
+      <c r="H32" s="4"/>
+      <c r="I32" s="36">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="2:11" ht="14.25">
+      <c r="L32" s="2"/>
+    </row>
+    <row r="33" spans="2:12" ht="14.25">
       <c r="B33" s="6">
         <v>28</v>
       </c>
-      <c r="C33" s="36" t="s">
-        <v>6</v>
+      <c r="C33" s="35" t="s">
+        <v>45</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E33" s="5">
         <v>3</v>
@@ -1575,23 +1959,24 @@
       <c r="G33" s="5">
         <v>3</v>
       </c>
-      <c r="H33" s="39">
+      <c r="H33" s="5"/>
+      <c r="I33" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="2:11" ht="14.25">
+      <c r="L33" s="2"/>
+    </row>
+    <row r="34" spans="2:12" ht="14.25">
       <c r="B34" s="6">
         <v>29</v>
       </c>
-      <c r="C34" s="35" t="s">
-        <v>7</v>
+      <c r="C34" s="34" t="s">
+        <v>46</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E34" s="4">
         <v>3</v>
@@ -1602,150 +1987,161 @@
       <c r="G34" s="4">
         <v>3</v>
       </c>
-      <c r="H34" s="39">
+      <c r="H34" s="4"/>
+      <c r="I34" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-    </row>
-    <row r="35" spans="2:11" ht="14.25">
+      <c r="L34" s="2"/>
+    </row>
+    <row r="35" spans="2:12" ht="14.25">
       <c r="B35" s="6">
         <v>30</v>
       </c>
-      <c r="C35" s="35" t="s">
+      <c r="C35" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" s="23" t="s">
         <v>8</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>15</v>
       </c>
       <c r="E35" s="5">
         <v>2</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G35" s="5">
         <v>4</v>
       </c>
-      <c r="H35" s="39">
+      <c r="H35" s="5"/>
+      <c r="I35" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="2:11" ht="14.25">
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" spans="2:12" ht="14.25">
       <c r="B36" s="6">
         <v>31</v>
       </c>
-      <c r="C36" s="40" t="s">
-        <v>9</v>
+      <c r="C36" s="38" t="s">
+        <v>48</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E36" s="4">
         <v>2</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G36" s="4">
         <v>5</v>
       </c>
-      <c r="H36" s="41">
+      <c r="H36" s="4"/>
+      <c r="I36" s="39">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="2:11" ht="15">
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="2:12" ht="15">
       <c r="B37" s="6">
         <v>32</v>
       </c>
-      <c r="C37" s="33" t="s">
-        <v>10</v>
+      <c r="C37" s="51" t="s">
+        <v>49</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E37" s="5">
         <v>3</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G37" s="5">
         <v>4</v>
       </c>
-      <c r="H37" s="38">
+      <c r="H37" s="5"/>
+      <c r="I37" s="36">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="2:11" ht="15">
+      <c r="L37" s="2"/>
+    </row>
+    <row r="38" spans="2:12" ht="15">
       <c r="B38" s="6">
         <v>33</v>
       </c>
       <c r="C38" s="32" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E38" s="4">
         <v>5</v>
       </c>
       <c r="F38" s="27" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G38" s="4">
         <v>2</v>
       </c>
-      <c r="H38" s="38">
+      <c r="H38" s="4"/>
+      <c r="I38" s="36">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" ht="14.25">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" ht="14.25">
       <c r="B39" s="7">
         <v>34</v>
       </c>
-      <c r="C39" s="37" t="s">
-        <v>12</v>
+      <c r="C39" s="49" t="s">
+        <v>52</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E39" s="5">
         <v>3</v>
       </c>
-      <c r="F39" s="49" t="s">
-        <v>21</v>
+      <c r="F39" s="47" t="s">
+        <v>14</v>
       </c>
       <c r="G39" s="5">
         <v>1</v>
       </c>
-      <c r="H39" s="39">
+      <c r="H39" s="5"/>
+      <c r="I39" s="37">
         <f>E39*G39</f>
         <v>3</v>
       </c>
-      <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="K7:K11"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="K5:L6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/_ANALISIS DE RIESGOS.xlsx
+++ b/_ANALISIS DE RIESGOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9999b953125d8be8/Desktop/TALLER/Proyecto-IS1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="13_ncr:1_{C1F22416-6BDA-44B7-8828-8F9AD7764DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FDB0FF9-B2E6-47CC-8BB5-1C8931A3ABB2}"/>
+  <xr:revisionPtr revIDLastSave="351" documentId="13_ncr:1_{C1F22416-6BDA-44B7-8828-8F9AD7764DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7C7D48B-82B5-4CB0-B0E4-563102840E66}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="64">
   <si>
     <t>RIESGO</t>
   </si>
@@ -219,6 +219,12 @@
   </si>
   <si>
     <t>Intolerable</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Tolerable</t>
   </si>
 </sst>
 </file>
@@ -314,7 +320,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -468,6 +474,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
@@ -672,7 +684,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -737,31 +749,6 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -787,9 +774,37 @@
     <xf numFmtId="0" fontId="12" fillId="25" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -805,6 +820,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1057,17 +1076,17 @@
         <v>53</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="57" t="s">
+      <c r="K5" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="58"/>
-      <c r="M5" s="55" t="s">
+      <c r="L5" s="73"/>
+      <c r="M5" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="56"/>
+      <c r="N5" s="70"/>
+      <c r="O5" s="70"/>
+      <c r="P5" s="70"/>
+      <c r="Q5" s="71"/>
     </row>
     <row r="6" spans="1:17" ht="15">
       <c r="B6" s="6">
@@ -1088,7 +1107,7 @@
       <c r="G6" s="4">
         <v>4</v>
       </c>
-      <c r="H6" s="77" t="s">
+      <c r="H6" s="67" t="s">
         <v>54</v>
       </c>
       <c r="I6" s="36">
@@ -1096,21 +1115,21 @@
         <v>12</v>
       </c>
       <c r="J6" s="2"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="66" t="s">
+      <c r="K6" s="74"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="67" t="s">
+      <c r="N6" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="O6" s="68" t="s">
+      <c r="O6" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="Q6" s="70" t="s">
+      <c r="Q6" s="61" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1141,25 +1160,25 @@
         <v>6</v>
       </c>
       <c r="J7" s="2"/>
-      <c r="K7" s="53" t="s">
+      <c r="K7" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="61" t="s">
+      <c r="L7" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="71" t="s">
+      <c r="M7" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="N7" s="71" t="s">
+      <c r="N7" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="O7" s="71" t="s">
+      <c r="O7" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="P7" s="72" t="s">
+      <c r="P7" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="Q7" s="73" t="s">
+      <c r="Q7" s="64" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1182,7 +1201,7 @@
       <c r="G8" s="4">
         <v>3</v>
       </c>
-      <c r="H8" s="52" t="s">
+      <c r="H8" s="76" t="s">
         <v>60</v>
       </c>
       <c r="I8" s="37">
@@ -1190,23 +1209,23 @@
         <v>6</v>
       </c>
       <c r="J8" s="2"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="62" t="s">
+      <c r="K8" s="68"/>
+      <c r="L8" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="71" t="s">
+      <c r="M8" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="N8" s="71" t="s">
+      <c r="N8" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="O8" s="72" t="s">
+      <c r="O8" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="P8" s="73" t="s">
+      <c r="P8" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="Q8" s="74" t="s">
+      <c r="Q8" s="65" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1229,7 +1248,7 @@
       <c r="G9" s="5">
         <v>3</v>
       </c>
-      <c r="H9" s="77" t="s">
+      <c r="H9" s="67" t="s">
         <v>54</v>
       </c>
       <c r="I9" s="36">
@@ -1237,23 +1256,23 @@
         <v>12</v>
       </c>
       <c r="J9" s="2"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="63" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" s="72" t="s">
+      <c r="K9" s="68"/>
+      <c r="L9" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="N9" s="72" t="s">
+      <c r="N9" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="O9" s="73" t="s">
+      <c r="O9" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="P9" s="74" t="s">
+      <c r="P9" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="Q9" s="75" t="s">
+      <c r="Q9" s="66" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1276,7 +1295,7 @@
       <c r="G10" s="4">
         <v>5</v>
       </c>
-      <c r="H10" s="78" t="s">
+      <c r="H10" s="77" t="s">
         <v>61</v>
       </c>
       <c r="I10" s="36">
@@ -1284,23 +1303,23 @@
         <v>20</v>
       </c>
       <c r="J10" s="2"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="64" t="s">
+      <c r="K10" s="68"/>
+      <c r="L10" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="M10" s="73" t="s">
+      <c r="M10" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="N10" s="73" t="s">
+      <c r="N10" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="74" t="s">
+      <c r="O10" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="P10" s="75" t="s">
+      <c r="P10" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="Q10" s="75" t="s">
+      <c r="Q10" s="66" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1323,7 +1342,7 @@
       <c r="G11" s="5">
         <v>3</v>
       </c>
-      <c r="H11" s="77" t="s">
+      <c r="H11" s="67" t="s">
         <v>54</v>
       </c>
       <c r="I11" s="36">
@@ -1331,23 +1350,23 @@
         <v>15</v>
       </c>
       <c r="J11" s="2"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="65" t="s">
+      <c r="K11" s="69"/>
+      <c r="L11" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="73" t="s">
+      <c r="M11" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="N11" s="74" t="s">
+      <c r="N11" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="O11" s="75" t="s">
+      <c r="O11" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="P11" s="75" t="s">
+      <c r="P11" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="Q11" s="75" t="s">
+      <c r="Q11" s="66" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1370,7 +1389,9 @@
       <c r="G12" s="4">
         <v>4</v>
       </c>
-      <c r="H12" s="4"/>
+      <c r="H12" s="76" t="s">
+        <v>60</v>
+      </c>
       <c r="I12" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1398,7 +1419,9 @@
       <c r="G13" s="5">
         <v>3</v>
       </c>
-      <c r="H13" s="5"/>
+      <c r="H13" s="76" t="s">
+        <v>60</v>
+      </c>
       <c r="I13" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1427,7 +1450,9 @@
       <c r="G14" s="4">
         <v>5</v>
       </c>
-      <c r="H14" s="4"/>
+      <c r="H14" s="77" t="s">
+        <v>61</v>
+      </c>
       <c r="I14" s="36">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1455,7 +1480,9 @@
       <c r="G15" s="5">
         <v>3</v>
       </c>
-      <c r="H15" s="5"/>
+      <c r="H15" s="78" t="s">
+        <v>62</v>
+      </c>
       <c r="I15" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1483,7 +1510,9 @@
       <c r="G16" s="4">
         <v>2</v>
       </c>
-      <c r="H16" s="4"/>
+      <c r="H16" s="76" t="s">
+        <v>60</v>
+      </c>
       <c r="I16" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1511,7 +1540,9 @@
       <c r="G17" s="5">
         <v>1</v>
       </c>
-      <c r="H17" s="5"/>
+      <c r="H17" s="79" t="s">
+        <v>63</v>
+      </c>
       <c r="I17" s="37">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1539,7 +1570,9 @@
       <c r="G18" s="4">
         <v>1</v>
       </c>
-      <c r="H18" s="4"/>
+      <c r="H18" s="78" t="s">
+        <v>62</v>
+      </c>
       <c r="I18" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1567,7 +1600,9 @@
       <c r="G19" s="5">
         <v>3</v>
       </c>
-      <c r="H19" s="5"/>
+      <c r="H19" s="67" t="s">
+        <v>54</v>
+      </c>
       <c r="I19" s="36">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1595,7 +1630,9 @@
       <c r="G20" s="4">
         <v>2</v>
       </c>
-      <c r="H20" s="4"/>
+      <c r="H20" s="76" t="s">
+        <v>60</v>
+      </c>
       <c r="I20" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1623,7 +1660,9 @@
       <c r="G21" s="5">
         <v>5</v>
       </c>
-      <c r="H21" s="5"/>
+      <c r="H21" s="77" t="s">
+        <v>61</v>
+      </c>
       <c r="I21" s="36">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1651,7 +1690,9 @@
       <c r="G22" s="4">
         <v>3</v>
       </c>
-      <c r="H22" s="4"/>
+      <c r="H22" s="67" t="s">
+        <v>54</v>
+      </c>
       <c r="I22" s="36">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1679,7 +1720,9 @@
       <c r="G23" s="5">
         <v>3</v>
       </c>
-      <c r="H23" s="5"/>
+      <c r="H23" s="78" t="s">
+        <v>62</v>
+      </c>
       <c r="I23" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1707,7 +1750,9 @@
       <c r="G24" s="4">
         <v>4</v>
       </c>
-      <c r="H24" s="4"/>
+      <c r="H24" s="76" t="s">
+        <v>60</v>
+      </c>
       <c r="I24" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1735,7 +1780,9 @@
       <c r="G25" s="5">
         <v>4</v>
       </c>
-      <c r="H25" s="5"/>
+      <c r="H25" s="78" t="s">
+        <v>62</v>
+      </c>
       <c r="I25" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1763,7 +1810,9 @@
       <c r="G26" s="4">
         <v>3</v>
       </c>
-      <c r="H26" s="4"/>
+      <c r="H26" s="78" t="s">
+        <v>62</v>
+      </c>
       <c r="I26" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1791,7 +1840,9 @@
       <c r="G27" s="5">
         <v>4</v>
       </c>
-      <c r="H27" s="5"/>
+      <c r="H27" s="78" t="s">
+        <v>62</v>
+      </c>
       <c r="I27" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1819,7 +1870,9 @@
       <c r="G28" s="4">
         <v>5</v>
       </c>
-      <c r="H28" s="4"/>
+      <c r="H28" s="77" t="s">
+        <v>61</v>
+      </c>
       <c r="I28" s="36">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1847,7 +1900,9 @@
       <c r="G29" s="5">
         <v>1</v>
       </c>
-      <c r="H29" s="5"/>
+      <c r="H29" s="78" t="s">
+        <v>62</v>
+      </c>
       <c r="I29" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1875,7 +1930,9 @@
       <c r="G30" s="4">
         <v>1</v>
       </c>
-      <c r="H30" s="4"/>
+      <c r="H30" s="78" t="s">
+        <v>62</v>
+      </c>
       <c r="I30" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1903,7 +1960,9 @@
       <c r="G31" s="5">
         <v>3</v>
       </c>
-      <c r="H31" s="5"/>
+      <c r="H31" s="78" t="s">
+        <v>62</v>
+      </c>
       <c r="I31" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1931,7 +1990,9 @@
       <c r="G32" s="4">
         <v>3</v>
       </c>
-      <c r="H32" s="4"/>
+      <c r="H32" s="67" t="s">
+        <v>54</v>
+      </c>
       <c r="I32" s="36">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1959,7 +2020,9 @@
       <c r="G33" s="5">
         <v>3</v>
       </c>
-      <c r="H33" s="5"/>
+      <c r="H33" s="78" t="s">
+        <v>62</v>
+      </c>
       <c r="I33" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1987,7 +2050,9 @@
       <c r="G34" s="4">
         <v>3</v>
       </c>
-      <c r="H34" s="4"/>
+      <c r="H34" s="78" t="s">
+        <v>62</v>
+      </c>
       <c r="I34" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2015,7 +2080,9 @@
       <c r="G35" s="5">
         <v>4</v>
       </c>
-      <c r="H35" s="5"/>
+      <c r="H35" s="78" t="s">
+        <v>62</v>
+      </c>
       <c r="I35" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2043,7 +2110,9 @@
       <c r="G36" s="4">
         <v>5</v>
       </c>
-      <c r="H36" s="4"/>
+      <c r="H36" s="81" t="s">
+        <v>54</v>
+      </c>
       <c r="I36" s="39">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2071,7 +2140,9 @@
       <c r="G37" s="5">
         <v>4</v>
       </c>
-      <c r="H37" s="5"/>
+      <c r="H37" s="67" t="s">
+        <v>54</v>
+      </c>
       <c r="I37" s="36">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2099,7 +2170,9 @@
       <c r="G38" s="4">
         <v>2</v>
       </c>
-      <c r="H38" s="4"/>
+      <c r="H38" s="80" t="s">
+        <v>62</v>
+      </c>
       <c r="I38" s="36">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2127,7 +2200,9 @@
       <c r="G39" s="5">
         <v>1</v>
       </c>
-      <c r="H39" s="5"/>
+      <c r="H39" s="79" t="s">
+        <v>63</v>
+      </c>
       <c r="I39" s="37">
         <f>E39*G39</f>
         <v>3</v>
